--- a/data/M2-IEAP-ICDSP.xlsx
+++ b/data/M2-IEAP-ICDSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olivier/SSDS/enseignement/UFR STAPS/Direction/Outils/celcatreport/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olivier/SSDS/direction/Outils/celcatreport/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A01424-077F-D44F-8DA4-C8747AABCE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2D4073-1A88-0443-8C93-BF1FA43B88D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="19700" xr2:uid="{154AE90F-D41B-8B49-BA91-D855BEB6F170}"/>
   </bookViews>
@@ -591,7 +591,7 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -623,7 +623,7 @@
         <v>10</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -655,7 +655,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -687,7 +687,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -719,7 +719,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -751,7 +751,7 @@
         <v>16</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -815,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -847,7 +847,7 @@
         <v>8</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -879,7 +879,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -937,13 +937,13 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -969,13 +969,13 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
